--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="D2">
-        <v>104</v>
+        <v>251</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>2</v>
-      </c>
-      <c r="G2">
-        <v>100</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="D3">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>236</v>
       </c>
       <c r="D3">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
